--- a/business_forms/042_subscription_renewal_approval_request_form--business_forms.xlsx
+++ b/business_forms/042_subscription_renewal_approval_request_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,8 +773,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -802,12 +802,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'approve',_'value':_'approve'}</t>
+          <t>approve</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Approve', 'value': 'Approve'}</t>
+          <t>Approve</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'deny',_'value':_'deny'}</t>
+          <t>deny</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Deny', 'value': 'Deny'}</t>
+          <t>Deny</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'request_for_review',_'value':_'request_for_review'}</t>
+          <t>request_for_review</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Request for Review', 'value': 'Request for Review'}</t>
+          <t>Request for Review</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'renewal_request',_'value':_'renewal_request'}</t>
+          <t>renewal_request</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Renewal Request', 'value': 'Renewal Request'}</t>
+          <t>Renewal Request</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'subscription_renewal_approval_request',_'value':_'subscription_renewal_approval_request'}</t>
+          <t>subscription_renewal_approval_request</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Subscription Renewal Approval Request', 'value': 'Subscription Renewal Approval Request'}</t>
+          <t>Subscription Renewal Approval Request</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'approved',_'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Approved', 'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'not_approved',_'value':_'not_approved'}</t>
+          <t>not_approved</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'Not Approved', 'value': 'Not Approved'}</t>
+          <t>Not Approved</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'approved_with_comments',_'value':_'approved_with_comments'}</t>
+          <t>approved_with_comments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'Approved with Comments', 'value': 'Approved with Comments'}</t>
+          <t>Approved with Comments</t>
         </is>
       </c>
     </row>
